--- a/docs/Product/Personal_Library_Manager_User_Stories.xlsx
+++ b/docs/Product/Personal_Library_Manager_User_Stories.xlsx
@@ -8,20 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PersonalLibraryManager Project\docs\Product\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EE6D695-B5AA-40F1-8864-80F4B39DAA5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D23F60D8-919E-40D0-B0F5-C4881AD76C6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1848" yWindow="1848" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="User Stories" sheetId="1" r:id="rId1"/>
     <sheet name="Overview" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <calcPr calcId="191029" iterateDelta="1E-4" forceFullCalc="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="745" uniqueCount="360">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="910" uniqueCount="461">
   <si>
     <t>Story</t>
   </si>
@@ -85,7 +85,10 @@
     <t>M0 — Foundation</t>
   </si>
   <si>
-    <t>Not Started</t>
+    <t>Implemented by registration validation, ASP.NET Core Identity and confirmation-email dispatch.</t>
+  </si>
+  <si>
+    <t>Done</t>
   </si>
   <si>
     <t>US-002</t>
@@ -105,6 +108,9 @@
 • Invalid or expired token returns a clear error</t>
   </si>
   <si>
+    <t>Implemented by GET /api/auth/confirm-email and Identity email tokens.</t>
+  </si>
+  <si>
     <t>US-003</t>
   </si>
   <si>
@@ -119,6 +125,9 @@
 • Protected endpoints require authentication</t>
   </si>
   <si>
+    <t>Implemented by POST /api/auth/login, JWT issuance and protected controllers.</t>
+  </si>
+  <si>
     <t>US-004</t>
   </si>
   <si>
@@ -136,13 +145,76 @@
 • Refresh token rotation or revocation is enforced</t>
   </si>
   <si>
+    <t>Implemented by POST /api/auth/refresh with refresh-token rotation and revocation.</t>
+  </si>
+  <si>
+    <t>US-005</t>
+  </si>
+  <si>
+    <t>request a new email-confirmation message</t>
+  </si>
+  <si>
+    <t>I can finish verification when the original message is unavailable</t>
+  </si>
+  <si>
+    <t>• An unconfirmed account receives a new confirmation challenge
+• Confirmed and unknown accounts do not reveal account state
+• The endpoint returns a safe, consistent response</t>
+  </si>
+  <si>
+    <t>Implemented by POST /api/auth/resend-confirmation and AuthService.</t>
+  </si>
+  <si>
+    <t>US-006</t>
+  </si>
+  <si>
+    <t>log out of my current refresh-token session</t>
+  </si>
+  <si>
+    <t>a lost token cannot keep creating access tokens</t>
+  </si>
+  <si>
+    <t>• Logout requires an authenticated user
+• The supplied refresh-token session is revoked
+• A revoked refresh token cannot be used again</t>
+  </si>
+  <si>
+    <t>Implemented by POST /api/auth/logout with refresh-session revocation.</t>
+  </si>
+  <si>
+    <t>US-007</t>
+  </si>
+  <si>
+    <t>API platform</t>
+  </si>
+  <si>
+    <t>Developer</t>
+  </si>
+  <si>
+    <t>API client developer</t>
+  </si>
+  <si>
+    <t>receive consistent success and failure responses</t>
+  </si>
+  <si>
+    <t>the client can handle API outcomes predictably</t>
+  </si>
+  <si>
+    <t>• Successful responses use the common API envelope
+• Validation errors include field-level details
+• Authentication, authorization and not-found failures use stable codes and a trace identifier</t>
+  </si>
+  <si>
+    <t>Should Have</t>
+  </si>
+  <si>
+    <t>Implemented by ApiResponse, API behavior configuration and GlobalExceptionMiddleware.</t>
+  </si>
+  <si>
+    <t>US-008</t>
+  </si>
+  <si>
     <t>Library</t>
-  </si>
-  <si>
-    <t>M1 — Core Library</t>
-  </si>
-  <si>
-    <t>US-008</t>
   </si>
   <si>
     <t>Library owner</t>
@@ -159,18 +231,27 @@
 • Unauthorized users cannot update it</t>
   </si>
   <si>
+    <t>M1 — Core Library</t>
+  </si>
+  <si>
+    <t>Implemented by PATCH /api/libraries/{libraryId} with owner/editor authorization.</t>
+  </si>
+  <si>
     <t>US-009</t>
   </si>
   <si>
-    <t>have a personal library available</t>
-  </si>
-  <si>
-    <t>I can start cataloguing without being blocked</t>
-  </si>
-  <si>
-    <t>• User can create at least one personal library
-• App handles users with no libraries by offering creation
-• Library ownership is associated with the user</t>
+    <t>create a personal library</t>
+  </si>
+  <si>
+    <t>I can start cataloguing my own collection</t>
+  </si>
+  <si>
+    <t>• An authenticated user can create a library with a valid name
+• Private visibility is used when no visibility is supplied
+• The creator is recorded as the Owner member</t>
+  </si>
+  <si>
+    <t>Implemented by POST /api/libraries with creator ownership.</t>
   </si>
   <si>
     <t>US-010</t>
@@ -193,6 +274,9 @@
 • Owner role is recorded for the creator</t>
   </si>
   <si>
+    <t>Implemented by library membership checks and owner/editor/viewer enforcement.</t>
+  </si>
+  <si>
     <t>US-011</t>
   </si>
   <si>
@@ -213,6 +297,9 @@
 • Saved author is available for book association</t>
   </si>
   <si>
+    <t>Implemented by POST /api/authors.</t>
+  </si>
+  <si>
     <t>US-012</t>
   </si>
   <si>
@@ -227,6 +314,9 @@
 • Saved publisher can be referenced by editions</t>
   </si>
   <si>
+    <t>Implemented by POST /api/publishers.</t>
+  </si>
+  <si>
     <t>US-013</t>
   </si>
   <si>
@@ -241,6 +331,9 @@
 • Book is stored independently from its editions</t>
   </si>
   <si>
+    <t>Implemented by POST /api/books with work-level metadata.</t>
+  </si>
+  <si>
     <t>US-014</t>
   </si>
   <si>
@@ -253,6 +346,9 @@
     <t>• Existing authors can be linked to a book
 • AuthorOrder is retained
 • Duplicate book-author associations are prevented</t>
+  </si>
+  <si>
+    <t>Implemented by ordered BookAuthor associations with duplicate validation.</t>
   </si>
   <si>
     <t>US-015</t>
@@ -270,6 +366,9 @@
 • Multiple editions can belong to one book</t>
   </si>
   <si>
+    <t>Implemented by POST /api/editions with optional metadata and ISBN validation.</t>
+  </si>
+  <si>
     <t>US-016</t>
   </si>
   <si>
@@ -282,6 +381,9 @@
     <t>• Book title and authors are shown
 • Available editions and their identifiers are shown
 • Optional missing metadata does not break the response</t>
+  </si>
+  <si>
+    <t>Implemented by book and edition detail endpoints.</t>
   </si>
   <si>
     <t>US-017</t>
@@ -305,6 +407,9 @@
 • Unauthorized users cannot add copies</t>
   </si>
   <si>
+    <t>In Progress</t>
+  </si>
+  <si>
     <t>US-018</t>
   </si>
   <si>
@@ -319,6 +424,9 @@
 • Existing copies are not overwritten</t>
   </si>
   <si>
+    <t>Implemented by distinct BookCopy creation for repeated editions.</t>
+  </si>
+  <si>
     <t>US-019</t>
   </si>
   <si>
@@ -333,6 +441,9 @@
 • Empty library is handled</t>
   </si>
   <si>
+    <t>Implemented by GET /api/libraries/{libraryId}/books.</t>
+  </si>
+  <si>
     <t>US-020</t>
   </si>
   <si>
@@ -353,6 +464,9 @@
     <t>M2 — Smart ISBN</t>
   </si>
   <si>
+    <t>Implemented by IsbnNormalizer checksum validation and separator normalization.</t>
+  </si>
+  <si>
     <t>US-021</t>
   </si>
   <si>
@@ -367,6 +481,9 @@
 • Missing local edition proceeds to external lookup</t>
   </si>
   <si>
+    <t>Implemented by local-edition lookup before external providers.</t>
+  </si>
+  <si>
     <t>US-022</t>
   </si>
   <si>
@@ -384,6 +501,9 @@
 • Not-found and unavailable provider results are handled</t>
   </si>
   <si>
+    <t>Implemented by OpenLibraryMetadataProvider in the provider chain.</t>
+  </si>
+  <si>
     <t>US-023</t>
   </si>
   <si>
@@ -398,6 +518,9 @@
 • Provider-specific data does not leak into the domain model</t>
   </si>
   <si>
+    <t>Implemented by the common BookMetadata model and provider adapters.</t>
+  </si>
+  <si>
     <t>US-024</t>
   </si>
   <si>
@@ -412,7 +535,7 @@
 • All providers failing returns a clear no-result response</t>
   </si>
   <si>
-    <t>Should Have</t>
+    <t>Implemented by FallbackBookMetadataProvider across Google Books, Open Library and web search.</t>
   </si>
   <si>
     <t>US-025</t>
@@ -429,6 +552,9 @@
 • User can confirm or cancel</t>
   </si>
   <si>
+    <t>Implemented by GET /api/books/lookup/{isbn}; preview does not persist data.</t>
+  </si>
+  <si>
     <t>US-026</t>
   </si>
   <si>
@@ -446,6 +572,9 @@
 • Response indicates exact-edition ownership and number of copies</t>
   </si>
   <si>
+    <t>Implemented by library-scoped exact-edition ownership checks with copy count.</t>
+  </si>
+  <si>
     <t>US-027</t>
   </si>
   <si>
@@ -460,6 +589,9 @@
 • Owned edition details are available</t>
   </si>
   <si>
+    <t>Not Started</t>
+  </si>
+  <si>
     <t>US-028</t>
   </si>
   <si>
@@ -472,6 +604,9 @@
     <t>• No matching library copy returns not-owned status
 • An edition existing globally is not treated as owned
 • Result does not expose other libraries’ contents</t>
+  </si>
+  <si>
+    <t>Implemented by a library-scoped not-owned result without exposing other libraries.</t>
   </si>
   <si>
     <t>US-029</t>
@@ -492,6 +627,9 @@
 • Failure does not leave a partially imported copy</t>
   </si>
   <si>
+    <t>Catalogue import is transactional, but confirmation does not create the library copy in the same workflow.</t>
+  </si>
+  <si>
     <t>US-030</t>
   </si>
   <si>
@@ -506,6 +644,9 @@
 • User can save a copy without an ISBN</t>
   </si>
   <si>
+    <t>Manual catalogue and copy endpoints exist, but lookup failure does not return a guided manual-entry flow.</t>
+  </si>
+  <si>
     <t>US-031</t>
   </si>
   <si>
@@ -717,6 +858,9 @@
 • Parent/child locations are supported by the model</t>
   </si>
   <si>
+    <t>Location hierarchy and copy assignment exist in the model, but location management endpoints are missing.</t>
+  </si>
+  <si>
     <t>US-045</t>
   </si>
   <si>
@@ -858,6 +1002,9 @@
     <t>M6 — Production</t>
   </si>
   <si>
+    <t>Provider timeouts and fallback exist; bounded retry policies are not implemented.</t>
+  </si>
+  <si>
     <t>US-054</t>
   </si>
   <si>
@@ -895,6 +1042,9 @@
 • Credentials and tokens are not logged</t>
   </si>
   <si>
+    <t>Metadata-provider failures are logged and API errors carry trace IDs; broader structured request/import logging is missing.</t>
+  </si>
+  <si>
     <t>US-056</t>
   </si>
   <si>
@@ -926,6 +1076,9 @@
 • Tests run repeatably</t>
   </si>
   <si>
+    <t>Implemented by repeatable unit tests for identity, libraries, ISBN lookup and ownership rules.</t>
+  </si>
+  <si>
     <t>US-058</t>
   </si>
   <si>
@@ -1019,6 +1172,9 @@
 • Membership changes are authorized</t>
   </si>
   <si>
+    <t>Owner, Editor and Viewer roles are modeled and enforced; owner-facing membership assignment is missing.</t>
+  </si>
+  <si>
     <t>US-064</t>
   </si>
   <si>
@@ -1033,6 +1189,9 @@
 • Broader visibility modes follow configured permissions</t>
   </si>
   <si>
+    <t>Visibility is stored and editable; public, friends-only and broader visibility access rules are not implemented.</t>
+  </si>
+  <si>
     <t>US-065</t>
   </si>
   <si>
@@ -1169,6 +1328,168 @@
 • Notification delivery failures are handled</t>
   </si>
   <si>
+    <t>US-073</t>
+  </si>
+  <si>
+    <t>Library owner or editor</t>
+  </si>
+  <si>
+    <t>update a library description and visibility</t>
+  </si>
+  <si>
+    <t>the collection settings remain current</t>
+  </si>
+  <si>
+    <t>• Name, description and visibility support partial updates
+• Empty descriptions can be cleared intentionally
+• Invalid visibility values and unauthorized updates are rejected</t>
+  </si>
+  <si>
+    <t>Implemented by PATCH /api/libraries/{libraryId} and LibraryService.</t>
+  </si>
+  <si>
+    <t>US-074</t>
+  </si>
+  <si>
+    <t>list, search, sort and page through my libraries</t>
+  </si>
+  <si>
+    <t>I can find the collection I want to open</t>
+  </si>
+  <si>
+    <t>• Only libraries available to the current user are returned
+• Search covers library name and description
+• Paging metadata, stable sorting, role, member count and book count are returned</t>
+  </si>
+  <si>
+    <t>Implemented by GET /api/libraries and the paged library repository query.</t>
+  </si>
+  <si>
+    <t>US-075</t>
+  </si>
+  <si>
+    <t>update an author record</t>
+  </si>
+  <si>
+    <t>author information can be corrected and completed</t>
+  </si>
+  <si>
+    <t>• Name, biography and life dates can be updated
+• A death date before the birth date is rejected
+• Unknown authors return a clear not-found response</t>
+  </si>
+  <si>
+    <t>Implemented by PATCH /api/authors/{authorId}.</t>
+  </si>
+  <si>
+    <t>US-076</t>
+  </si>
+  <si>
+    <t>update a publisher record</t>
+  </si>
+  <si>
+    <t>publisher information remains accurate</t>
+  </si>
+  <si>
+    <t>• Publisher name and website can be updated
+• Invalid URLs and empty requests are rejected
+• Unknown publishers return a clear not-found response</t>
+  </si>
+  <si>
+    <t>Implemented by PATCH /api/publishers/{publisherId}.</t>
+  </si>
+  <si>
+    <t>US-077</t>
+  </si>
+  <si>
+    <t>update a book and its ordered authors</t>
+  </si>
+  <si>
+    <t>catalogue records can be corrected without duplicate author links</t>
+  </si>
+  <si>
+    <t>• Book metadata supports partial updates
+• Author order is retained when associations change
+• Unknown and duplicate author references are rejected</t>
+  </si>
+  <si>
+    <t>Implemented by PATCH /api/books/{bookId} and BookService.</t>
+  </si>
+  <si>
+    <t>US-078</t>
+  </si>
+  <si>
+    <t>update an edition record</t>
+  </si>
+  <si>
+    <t>edition metadata and identifiers remain accurate</t>
+  </si>
+  <si>
+    <t>• Edition, publisher, ISBN, language, date, pages, cover and description can be updated
+• ISBN checksums and related entity identifiers are validated
+• Unknown editions return a clear not-found response</t>
+  </si>
+  <si>
+    <t>Implemented by PATCH /api/editions/{editionId}.</t>
+  </si>
+  <si>
+    <t>US-079</t>
+  </si>
+  <si>
+    <t>Catalogue user</t>
+  </si>
+  <si>
+    <t>navigate books, authors, editions and publishers by relationship</t>
+  </si>
+  <si>
+    <t>I can explore the catalogue without duplicating data</t>
+  </si>
+  <si>
+    <t>• Books can be retrieved by author
+• Authors and editions can be retrieved by book
+• Publishers used by a book can be retrieved</t>
+  </si>
+  <si>
+    <t>Implemented by the catalogue relationship GET endpoints.</t>
+  </si>
+  <si>
+    <t>US-080</t>
+  </si>
+  <si>
+    <t>see metadata provenance and confirm web-search results</t>
+  </si>
+  <si>
+    <t>unverified metadata is not imported without review</t>
+  </si>
+  <si>
+    <t>• Lookup results identify their source and whether review is required
+• Web-search metadata includes source references
+• Import rejects review-required metadata without explicit confirmation</t>
+  </si>
+  <si>
+    <t>Implemented by metadata provenance, preview warnings and ConfirmWebMetadata validation.</t>
+  </si>
+  <si>
+    <t>US-081</t>
+  </si>
+  <si>
+    <t>System maintainer</t>
+  </si>
+  <si>
+    <t>import reviewed metadata atomically while reusing catalogue entities</t>
+  </si>
+  <si>
+    <t>concurrent or failed imports do not create partial duplicate data</t>
+  </si>
+  <si>
+    <t>• The ISBN is rechecked inside the transaction
+• Existing authors, publishers and matching books are reused
+• Book and edition changes commit together or roll back together</t>
+  </si>
+  <si>
+    <t>Implemented by BookMetadataLookupService transactional import.</t>
+  </si>
+  <si>
     <t>PERSONAL LIBRARY MANAGER | USER STORY BACKLOG</t>
   </si>
   <si>
@@ -1184,6 +1505,9 @@
     <t>Completed</t>
   </si>
   <si>
+    <t>In progress</t>
+  </si>
+  <si>
     <t>Stories</t>
   </si>
   <si>
@@ -1229,19 +1553,22 @@
     <t>Notes</t>
   </si>
   <si>
-    <t>Status is intentionally Not Started until you review and update it.</t>
-  </si>
-  <si>
-    <t>Priorities and acceptance criteria are proposed from your source documents; confirm implementation details as you build.</t>
-  </si>
-  <si>
-    <t>M0–M3 = MVP path; M4–M7 and Future = subsequent work.</t>
-  </si>
-  <si>
-    <t>Sources: ProductVision, Requirements, Milestones, Backlog, ERD, README (uploaded).</t>
-  </si>
-  <si>
-    <t>Done</t>
+    <t>Status reflects an audit of the repository completed on 20 October 2026.</t>
+  </si>
+  <si>
+    <t>Done means every acceptance criterion is implemented. In Progress identifies a partially implemented story.</t>
+  </si>
+  <si>
+    <t>M0–M3 are the MVP path. M4–M7 and Future remain subsequent work.</t>
+  </si>
+  <si>
+    <t>Sources: current API, application, domain, infrastructure, migrations, tests, README, and product documents.</t>
+  </si>
+  <si>
+    <t>Implemented by the manual catalogue endpoints and `POST /api/libraries/{libraryId}/books`. The frontend can create or select the book edition first, then add the copy. Format defaults to Other; reading status defaults to Unread, while location and notes are optional. Owner/editor access is enforced.</t>
+  </si>
+  <si>
+    <t>e</t>
   </si>
 </sst>
 </file>
@@ -1306,7 +1633,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1320,11 +1647,33 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="12">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE0E0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF3C4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFD8F3DC"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1367,6 +1716,27 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE6F0FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF3D7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFBE7E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1381,7 +1751,20 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="UserStoriesTable" displayName="UserStoriesTable" ref="A1:K70" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="UserStoriesTable" displayName="UserStoriesTable" ref="A1:K82" totalsRowShown="0">
+  <autoFilter ref="A1:K82" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}">
+    <filterColumn colId="8">
+      <filters>
+        <filter val="M2 — Smart ISBN"/>
+        <filter val="M4 — Organization"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="10">
+      <filters>
+        <filter val="In Progress"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Story"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Module"/>
@@ -1594,7 +1977,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K73"/>
+  <dimension ref="A1:K82"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -1645,7 +2028,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="103.95" customHeight="1">
+    <row r="2" spans="1:11" ht="103.95" hidden="1" customHeight="1">
       <c r="A2" s="3" t="s">
         <v>11</v>
       </c>
@@ -1673,14 +2056,16 @@
       <c r="I2" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="J2" s="2"/>
+      <c r="J2" s="2" t="s">
+        <v>20</v>
+      </c>
       <c r="K2" s="2" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" ht="103.95" customHeight="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="103.95" hidden="1" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>12</v>
@@ -1689,16 +2074,16 @@
         <v>13</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>18</v>
@@ -1706,14 +2091,16 @@
       <c r="I3" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="J3" s="2"/>
+      <c r="J3" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="K3" s="2" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="103.95" customHeight="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="103.95" hidden="1" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>12</v>
@@ -1722,16 +2109,16 @@
         <v>13</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>18</v>
@@ -1739,14 +2126,16 @@
       <c r="I4" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="J4" s="2"/>
+      <c r="J4" s="2" t="s">
+        <v>32</v>
+      </c>
       <c r="K4" s="2" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="103.95" customHeight="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="103.95" hidden="1" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>12</v>
@@ -1755,16 +2144,16 @@
         <v>13</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>18</v>
@@ -1772,311 +2161,331 @@
       <c r="I5" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="J5" s="2"/>
+      <c r="J5" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="K5" s="2" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="103.95" customHeight="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="103.95" hidden="1" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>18</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="J6" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>43</v>
+      </c>
       <c r="K6" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" ht="103.95" customHeight="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="103.95" hidden="1" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>18</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="J7" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>48</v>
+      </c>
       <c r="K7" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" ht="103.95" customHeight="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="103.95" hidden="1" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>13</v>
+        <v>51</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="J8" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>57</v>
+      </c>
       <c r="K8" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" ht="103.95" customHeight="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="103.95" hidden="1" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>18</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="J9" s="2"/>
+        <v>64</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>65</v>
+      </c>
       <c r="K9" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" ht="103.95" customHeight="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="103.95" hidden="1" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>18</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="J10" s="2"/>
+        <v>64</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>70</v>
+      </c>
       <c r="K10" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" ht="103.95" customHeight="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="103.95" hidden="1" customHeight="1">
       <c r="A11" s="3" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>18</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="J11" s="2"/>
+        <v>64</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>77</v>
+      </c>
       <c r="K11" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" ht="103.95" customHeight="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="103.95" hidden="1" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>54</v>
+        <v>80</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>18</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="J12" s="2"/>
+        <v>64</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>84</v>
+      </c>
       <c r="K12" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" ht="103.95" customHeight="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="103.95" hidden="1" customHeight="1">
       <c r="A13" s="3" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>54</v>
+        <v>80</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>18</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="J13" s="2"/>
+        <v>64</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>89</v>
+      </c>
       <c r="K13" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" ht="103.95" customHeight="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="103.95" hidden="1" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>54</v>
+        <v>80</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>18</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="J14" s="2"/>
+        <v>64</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>94</v>
+      </c>
       <c r="K14" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" ht="103.95" customHeight="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="103.95" hidden="1" customHeight="1">
       <c r="A15" s="3" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>79</v>
@@ -2088,28 +2497,30 @@
         <v>80</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>82</v>
+        <v>97</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>18</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="J15" s="2"/>
+        <v>64</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>99</v>
+      </c>
       <c r="K15" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" ht="103.95" customHeight="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="103.95" hidden="1" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>79</v>
@@ -2121,28 +2532,30 @@
         <v>80</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>18</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="J16" s="2"/>
+        <v>64</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>104</v>
+      </c>
       <c r="K16" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" ht="103.95" customHeight="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="103.95" hidden="1" customHeight="1">
       <c r="A17" s="3" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>79</v>
@@ -2151,1808 +2564,2281 @@
         <v>13</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>48</v>
+        <v>80</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>90</v>
+        <v>107</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>18</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="J17" s="2"/>
+        <v>64</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>109</v>
+      </c>
       <c r="K17" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" ht="103.95" customHeight="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="124.2" hidden="1">
       <c r="A18" s="3" t="s">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>93</v>
+        <v>111</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>48</v>
+        <v>112</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>95</v>
+        <v>114</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>96</v>
+        <v>115</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>18</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J18" s="2"/>
+        <v>64</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>459</v>
+      </c>
       <c r="K18" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" ht="103.95" customHeight="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="103.95" hidden="1" customHeight="1">
       <c r="A19" s="3" t="s">
-        <v>98</v>
+        <v>117</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>93</v>
+        <v>111</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>48</v>
+        <v>112</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>99</v>
+        <v>118</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>101</v>
+        <v>120</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>18</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J19" s="2"/>
+        <v>64</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>121</v>
+      </c>
       <c r="K19" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" ht="103.95" customHeight="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="103.95" hidden="1" customHeight="1">
       <c r="A20" s="3" t="s">
-        <v>102</v>
+        <v>122</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>104</v>
+        <v>123</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>105</v>
+        <v>124</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>106</v>
+        <v>125</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>18</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J20" s="2"/>
+        <v>64</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>126</v>
+      </c>
       <c r="K20" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" ht="103.95" customHeight="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="103.95" hidden="1" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>107</v>
+        <v>127</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>103</v>
+        <v>128</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>108</v>
+        <v>129</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>109</v>
+        <v>130</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>110</v>
+        <v>131</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>18</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J21" s="2"/>
+        <v>132</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>133</v>
+      </c>
       <c r="K21" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" ht="103.95" customHeight="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="103.95" hidden="1" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>111</v>
+        <v>134</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>103</v>
+        <v>128</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>112</v>
+        <v>135</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>113</v>
+        <v>136</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>114</v>
+        <v>137</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>115</v>
+        <v>18</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J22" s="2"/>
+        <v>132</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>138</v>
+      </c>
       <c r="K22" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" ht="103.95" customHeight="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="103.95" hidden="1" customHeight="1">
       <c r="A23" s="3" t="s">
-        <v>116</v>
+        <v>139</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>93</v>
+        <v>140</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>117</v>
+        <v>141</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>118</v>
+        <v>142</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>119</v>
+        <v>143</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>18</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J23" s="2"/>
+        <v>132</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>144</v>
+      </c>
       <c r="K23" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" ht="103.95" customHeight="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="103.95" hidden="1" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>120</v>
+        <v>145</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>121</v>
+        <v>140</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>122</v>
+        <v>146</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>123</v>
+        <v>147</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>124</v>
+        <v>148</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>18</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J24" s="2"/>
+        <v>132</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>149</v>
+      </c>
       <c r="K24" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" ht="103.95" customHeight="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" ht="103.95" hidden="1" customHeight="1">
       <c r="A25" s="3" t="s">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>121</v>
+        <v>140</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>126</v>
+        <v>151</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>127</v>
+        <v>152</v>
       </c>
       <c r="G25" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="K25" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="103.95" hidden="1" customHeight="1">
+      <c r="A26" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="B26" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="H25" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J25" s="2"/>
-      <c r="K25" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" ht="103.95" customHeight="1">
-      <c r="A26" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>121</v>
-      </c>
       <c r="C26" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>130</v>
+        <v>156</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>131</v>
+        <v>157</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>132</v>
+        <v>158</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>18</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J26" s="2"/>
+        <v>132</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>159</v>
+      </c>
       <c r="K26" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" ht="103.95" customHeight="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" ht="103.95" hidden="1" customHeight="1">
       <c r="A27" s="3" t="s">
-        <v>133</v>
+        <v>160</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>134</v>
+        <v>161</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>135</v>
+        <v>162</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>136</v>
+        <v>163</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>137</v>
+        <v>164</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>18</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J27" s="2"/>
+        <v>132</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>165</v>
+      </c>
       <c r="K27" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" ht="103.95" customHeight="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" ht="103.95" hidden="1" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>138</v>
+        <v>166</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>134</v>
+        <v>161</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>139</v>
+        <v>167</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>140</v>
+        <v>168</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>141</v>
+        <v>169</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>18</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>97</v>
+        <v>132</v>
       </c>
       <c r="J28" s="2"/>
       <c r="K28" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" ht="103.95" customHeight="1">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="103.95" hidden="1" customHeight="1">
       <c r="A29" s="3" t="s">
-        <v>142</v>
+        <v>171</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>143</v>
+        <v>161</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>14</v>
+        <v>73</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>144</v>
+        <v>172</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>145</v>
+        <v>173</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>146</v>
+        <v>174</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>18</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="J29" s="2"/>
+        <v>132</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>175</v>
+      </c>
       <c r="K29" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="103.95" customHeight="1">
       <c r="A30" s="3" t="s">
-        <v>148</v>
+        <v>176</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>143</v>
+        <v>177</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>22</v>
+        <v>112</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>149</v>
+        <v>178</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>150</v>
+        <v>179</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>151</v>
+        <v>180</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>18</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="J30" s="2"/>
+        <v>132</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>181</v>
+      </c>
       <c r="K30" s="2" t="s">
-        <v>20</v>
+        <v>116</v>
       </c>
     </row>
     <row r="31" spans="1:11" ht="103.95" customHeight="1">
       <c r="A31" s="3" t="s">
-        <v>152</v>
+        <v>182</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>143</v>
+        <v>177</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>31</v>
+        <v>73</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>153</v>
+        <v>183</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>154</v>
+        <v>184</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>155</v>
+        <v>185</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>18</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="J31" s="2"/>
+        <v>460</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>186</v>
+      </c>
       <c r="K31" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" ht="103.95" customHeight="1">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" ht="103.95" hidden="1" customHeight="1">
       <c r="A32" s="3" t="s">
-        <v>156</v>
+        <v>187</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>143</v>
+        <v>188</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>157</v>
+        <v>189</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>158</v>
+        <v>190</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>159</v>
+        <v>191</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>18</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>147</v>
+        <v>192</v>
       </c>
       <c r="J32" s="2"/>
       <c r="K32" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" ht="103.95" customHeight="1">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" ht="103.95" hidden="1" customHeight="1">
       <c r="A33" s="3" t="s">
-        <v>160</v>
+        <v>193</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>143</v>
+        <v>188</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>161</v>
+        <v>194</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>162</v>
+        <v>195</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>163</v>
+        <v>196</v>
       </c>
       <c r="H33" s="2" t="s">
         <v>18</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>147</v>
+        <v>192</v>
       </c>
       <c r="J33" s="2"/>
       <c r="K33" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" ht="103.95" customHeight="1">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" ht="103.95" hidden="1" customHeight="1">
       <c r="A34" s="3" t="s">
-        <v>164</v>
+        <v>197</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>143</v>
+        <v>188</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>165</v>
+        <v>198</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>166</v>
+        <v>199</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>167</v>
+        <v>200</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>18</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>147</v>
+        <v>192</v>
       </c>
       <c r="J34" s="2"/>
       <c r="K34" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" ht="103.95" customHeight="1">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" ht="103.95" hidden="1" customHeight="1">
       <c r="A35" s="3" t="s">
-        <v>168</v>
+        <v>201</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>143</v>
+        <v>188</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>169</v>
+        <v>202</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>170</v>
+        <v>203</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>171</v>
+        <v>204</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>18</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>147</v>
+        <v>192</v>
       </c>
       <c r="J35" s="2"/>
       <c r="K35" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" ht="103.95" customHeight="1">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" ht="103.95" hidden="1" customHeight="1">
       <c r="A36" s="3" t="s">
-        <v>172</v>
+        <v>205</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>143</v>
+        <v>188</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>173</v>
+        <v>206</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>174</v>
+        <v>207</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>175</v>
+        <v>208</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>18</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>147</v>
+        <v>192</v>
       </c>
       <c r="J36" s="2"/>
       <c r="K36" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" ht="103.95" customHeight="1">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" ht="103.95" hidden="1" customHeight="1">
       <c r="A37" s="3" t="s">
-        <v>176</v>
+        <v>209</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>178</v>
+        <v>210</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>179</v>
+        <v>211</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>180</v>
+        <v>212</v>
       </c>
       <c r="H37" s="2" t="s">
         <v>18</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="J37" s="2"/>
       <c r="K37" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" ht="103.95" customHeight="1">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" ht="103.95" hidden="1" customHeight="1">
       <c r="A38" s="3" t="s">
-        <v>182</v>
+        <v>213</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>183</v>
+        <v>214</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>184</v>
+        <v>215</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>185</v>
+        <v>216</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>18</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="J38" s="2"/>
       <c r="K38" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" ht="103.95" customHeight="1">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" ht="103.95" hidden="1" customHeight="1">
       <c r="A39" s="3" t="s">
-        <v>186</v>
+        <v>217</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>187</v>
+        <v>218</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>188</v>
+        <v>219</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>189</v>
+        <v>220</v>
       </c>
       <c r="H39" s="2" t="s">
         <v>18</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="J39" s="2"/>
       <c r="K39" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" ht="103.95" customHeight="1">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" ht="103.95" hidden="1" customHeight="1">
       <c r="A40" s="3" t="s">
-        <v>190</v>
+        <v>221</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>177</v>
+        <v>222</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>191</v>
+        <v>223</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>192</v>
+        <v>224</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>193</v>
+        <v>225</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>18</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>181</v>
+        <v>226</v>
       </c>
       <c r="J40" s="2"/>
       <c r="K40" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11" ht="103.95" customHeight="1">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" ht="103.95" hidden="1" customHeight="1">
       <c r="A41" s="3" t="s">
-        <v>194</v>
+        <v>227</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>79</v>
+        <v>222</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>195</v>
+        <v>228</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>196</v>
+        <v>229</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>197</v>
+        <v>230</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>18</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>181</v>
+        <v>226</v>
       </c>
       <c r="J41" s="2"/>
       <c r="K41" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11" ht="103.95" customHeight="1">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" ht="103.95" hidden="1" customHeight="1">
       <c r="A42" s="3" t="s">
-        <v>198</v>
+        <v>231</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>199</v>
+        <v>222</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>200</v>
+        <v>232</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>201</v>
+        <v>233</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>202</v>
+        <v>234</v>
       </c>
       <c r="H42" s="2" t="s">
         <v>18</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>181</v>
+        <v>226</v>
       </c>
       <c r="J42" s="2"/>
       <c r="K42" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11" ht="103.95" customHeight="1">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" ht="103.95" hidden="1" customHeight="1">
       <c r="A43" s="3" t="s">
-        <v>203</v>
+        <v>235</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>79</v>
+        <v>222</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>204</v>
+        <v>236</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>205</v>
+        <v>237</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>206</v>
+        <v>238</v>
       </c>
       <c r="H43" s="2" t="s">
         <v>18</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>181</v>
+        <v>226</v>
       </c>
       <c r="J43" s="2"/>
       <c r="K43" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11" ht="103.95" customHeight="1">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" ht="103.95" hidden="1" customHeight="1">
       <c r="A44" s="3" t="s">
-        <v>207</v>
+        <v>239</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>80</v>
+        <v>112</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>209</v>
+        <v>241</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>210</v>
+        <v>242</v>
       </c>
       <c r="H44" s="2" t="s">
         <v>18</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>181</v>
+        <v>226</v>
       </c>
       <c r="J44" s="2"/>
       <c r="K44" s="2" t="s">
-        <v>20</v>
+        <v>170</v>
       </c>
     </row>
     <row r="45" spans="1:11" ht="103.95" customHeight="1">
       <c r="A45" s="3" t="s">
-        <v>211</v>
+        <v>243</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>177</v>
+        <v>244</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>48</v>
+        <v>112</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>212</v>
+        <v>245</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>213</v>
+        <v>246</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>214</v>
+        <v>247</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>18</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="J45" s="2"/>
+        <v>226</v>
+      </c>
+      <c r="J45" s="2" t="s">
+        <v>248</v>
+      </c>
       <c r="K45" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11" ht="103.95" customHeight="1">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" ht="103.95" hidden="1" customHeight="1">
       <c r="A46" s="3" t="s">
-        <v>215</v>
+        <v>249</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>216</v>
+        <v>111</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>48</v>
+        <v>112</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>217</v>
+        <v>250</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>218</v>
+        <v>251</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>219</v>
+        <v>252</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>220</v>
+        <v>18</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="J46" s="2"/>
       <c r="K46" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11" ht="103.95" customHeight="1">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" ht="103.95" hidden="1" customHeight="1">
       <c r="A47" s="3" t="s">
-        <v>222</v>
+        <v>253</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>216</v>
+        <v>111</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>48</v>
+        <v>112</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>223</v>
+        <v>254</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>224</v>
+        <v>255</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>225</v>
+        <v>256</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>220</v>
+        <v>18</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="J47" s="2"/>
       <c r="K47" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11" ht="103.95" customHeight="1">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" ht="103.95" hidden="1" customHeight="1">
       <c r="A48" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I48" s="2" t="s">
         <v>226</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="F48" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="G48" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="H48" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="I48" s="2" t="s">
-        <v>221</v>
       </c>
       <c r="J48" s="2"/>
       <c r="K48" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11" ht="103.95" customHeight="1">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" ht="103.95" hidden="1" customHeight="1">
       <c r="A49" s="3" t="s">
-        <v>230</v>
+        <v>261</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>216</v>
+        <v>262</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>231</v>
+        <v>263</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>232</v>
+        <v>264</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>233</v>
+        <v>265</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>220</v>
+        <v>266</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>221</v>
+        <v>267</v>
       </c>
       <c r="J49" s="2"/>
       <c r="K49" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11" ht="103.95" customHeight="1">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" ht="103.95" hidden="1" customHeight="1">
       <c r="A50" s="3" t="s">
-        <v>234</v>
+        <v>268</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>216</v>
+        <v>262</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>235</v>
+        <v>269</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>236</v>
+        <v>270</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>237</v>
+        <v>271</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>220</v>
+        <v>266</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>221</v>
+        <v>267</v>
       </c>
       <c r="J50" s="2"/>
       <c r="K50" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11" ht="103.95" customHeight="1">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" ht="103.95" hidden="1" customHeight="1">
       <c r="A51" s="3" t="s">
-        <v>238</v>
+        <v>272</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>239</v>
+        <v>262</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>240</v>
+        <v>273</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>241</v>
+        <v>274</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>242</v>
+        <v>275</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>115</v>
+        <v>266</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>243</v>
+        <v>267</v>
       </c>
       <c r="J51" s="2"/>
       <c r="K51" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="52" spans="1:11" ht="103.95" customHeight="1">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" ht="103.95" hidden="1" customHeight="1">
       <c r="A52" s="3" t="s">
-        <v>244</v>
+        <v>276</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>245</v>
+        <v>262</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>246</v>
+        <v>277</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>247</v>
+        <v>278</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>248</v>
+        <v>279</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>220</v>
+        <v>266</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>243</v>
+        <v>267</v>
       </c>
       <c r="J52" s="2"/>
       <c r="K52" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="53" spans="1:11" ht="103.95" customHeight="1">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" ht="103.95" hidden="1" customHeight="1">
       <c r="A53" s="3" t="s">
-        <v>249</v>
+        <v>280</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>251</v>
+        <v>73</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>252</v>
+        <v>281</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>253</v>
+        <v>282</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>254</v>
+        <v>283</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>115</v>
+        <v>266</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>243</v>
+        <v>267</v>
       </c>
       <c r="J53" s="2"/>
       <c r="K53" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="54" spans="1:11" ht="103.95" customHeight="1">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" ht="103.95" hidden="1" customHeight="1">
       <c r="A54" s="3" t="s">
-        <v>255</v>
+        <v>284</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>250</v>
+        <v>285</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>251</v>
+        <v>73</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>256</v>
+        <v>286</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>257</v>
+        <v>287</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>258</v>
+        <v>288</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>115</v>
+        <v>56</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="J54" s="2"/>
+        <v>289</v>
+      </c>
+      <c r="J54" s="2" t="s">
+        <v>290</v>
+      </c>
       <c r="K54" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="55" spans="1:11" ht="103.95" customHeight="1">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" ht="103.95" hidden="1" customHeight="1">
       <c r="A55" s="3" t="s">
-        <v>259</v>
+        <v>291</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>260</v>
+        <v>292</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>251</v>
+        <v>73</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>261</v>
+        <v>293</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>262</v>
+        <v>294</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>263</v>
+        <v>295</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>115</v>
+        <v>266</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>243</v>
+        <v>289</v>
       </c>
       <c r="J55" s="2"/>
       <c r="K55" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="56" spans="1:11" ht="103.95" customHeight="1">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" ht="103.95" hidden="1" customHeight="1">
       <c r="A56" s="3" t="s">
-        <v>264</v>
+        <v>296</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>260</v>
+        <v>297</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>251</v>
+        <v>298</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>265</v>
+        <v>299</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>266</v>
+        <v>300</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>267</v>
+        <v>301</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>115</v>
+        <v>56</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="J56" s="2"/>
+        <v>289</v>
+      </c>
+      <c r="J56" s="2" t="s">
+        <v>302</v>
+      </c>
       <c r="K56" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="57" spans="1:11" ht="103.95" customHeight="1">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" ht="103.95" hidden="1" customHeight="1">
       <c r="A57" s="3" t="s">
-        <v>268</v>
+        <v>303</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>269</v>
+        <v>297</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>251</v>
+        <v>298</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>270</v>
+        <v>304</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>271</v>
+        <v>305</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>272</v>
+        <v>306</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>115</v>
+        <v>56</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>243</v>
+        <v>289</v>
       </c>
       <c r="J57" s="2"/>
       <c r="K57" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="58" spans="1:11" ht="103.95" customHeight="1">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" ht="103.95" hidden="1" customHeight="1">
       <c r="A58" s="3" t="s">
-        <v>273</v>
+        <v>307</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>269</v>
+        <v>308</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>251</v>
+        <v>298</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>274</v>
+        <v>309</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>275</v>
+        <v>310</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>276</v>
+        <v>311</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>115</v>
+        <v>56</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="J58" s="2"/>
+        <v>289</v>
+      </c>
+      <c r="J58" s="2" t="s">
+        <v>312</v>
+      </c>
       <c r="K58" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="59" spans="1:11" ht="103.95" customHeight="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" ht="103.95" hidden="1" customHeight="1">
       <c r="A59" s="3" t="s">
-        <v>277</v>
+        <v>313</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>269</v>
+        <v>308</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>251</v>
+        <v>298</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>278</v>
+        <v>314</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>279</v>
+        <v>315</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>280</v>
+        <v>316</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>115</v>
+        <v>56</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>243</v>
+        <v>289</v>
       </c>
       <c r="J59" s="2"/>
       <c r="K59" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="60" spans="1:11" ht="103.95" customHeight="1">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" ht="103.95" hidden="1" customHeight="1">
       <c r="A60" s="3" t="s">
-        <v>281</v>
+        <v>317</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>282</v>
+        <v>318</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>38</v>
+        <v>298</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>283</v>
+        <v>319</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>284</v>
+        <v>320</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>285</v>
+        <v>321</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>220</v>
+        <v>56</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="J60" s="2"/>
       <c r="K60" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="61" spans="1:11" ht="103.95" customHeight="1">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" ht="103.95" hidden="1" customHeight="1">
       <c r="A61" s="3" t="s">
-        <v>287</v>
+        <v>322</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>282</v>
+        <v>318</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>38</v>
+        <v>298</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>288</v>
+        <v>323</v>
       </c>
       <c r="F61" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="G61" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="I61" s="2" t="s">
         <v>289</v>
-      </c>
-      <c r="G61" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="H61" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="I61" s="2" t="s">
-        <v>286</v>
       </c>
       <c r="J61" s="2"/>
       <c r="K61" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="62" spans="1:11" ht="103.95" customHeight="1">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" ht="103.95" hidden="1" customHeight="1">
       <c r="A62" s="3" t="s">
-        <v>291</v>
+        <v>326</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>282</v>
+        <v>318</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>38</v>
+        <v>298</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>292</v>
+        <v>327</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>293</v>
+        <v>328</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>294</v>
+        <v>329</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>220</v>
+        <v>56</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="J62" s="2"/>
       <c r="K62" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="63" spans="1:11" ht="103.95" customHeight="1">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" ht="103.95" hidden="1" customHeight="1">
       <c r="A63" s="3" t="s">
-        <v>295</v>
+        <v>330</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>296</v>
+        <v>331</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>297</v>
+        <v>332</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>298</v>
+        <v>333</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>299</v>
+        <v>334</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>220</v>
+        <v>266</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>286</v>
+        <v>335</v>
       </c>
       <c r="J63" s="2"/>
       <c r="K63" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="64" spans="1:11" ht="103.95" customHeight="1">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" ht="103.95" hidden="1" customHeight="1">
       <c r="A64" s="3" t="s">
-        <v>300</v>
+        <v>336</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>296</v>
+        <v>331</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>301</v>
+        <v>337</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>302</v>
+        <v>338</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>303</v>
+        <v>339</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>220</v>
+        <v>266</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="J64" s="2"/>
+        <v>335</v>
+      </c>
+      <c r="J64" s="2" t="s">
+        <v>340</v>
+      </c>
       <c r="K64" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="65" spans="1:11" ht="103.95" customHeight="1">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" ht="103.95" hidden="1" customHeight="1">
       <c r="A65" s="3" t="s">
-        <v>304</v>
+        <v>341</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>305</v>
+        <v>331</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>306</v>
+        <v>342</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>307</v>
+        <v>343</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>308</v>
+        <v>344</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>220</v>
+        <v>266</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="J65" s="2"/>
+        <v>335</v>
+      </c>
+      <c r="J65" s="2" t="s">
+        <v>345</v>
+      </c>
       <c r="K65" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="66" spans="1:11" ht="103.95" customHeight="1">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" ht="103.95" hidden="1" customHeight="1">
       <c r="A66" s="3" t="s">
-        <v>309</v>
+        <v>346</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>310</v>
+        <v>347</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>22</v>
+        <v>73</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>311</v>
+        <v>348</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>312</v>
+        <v>349</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>313</v>
+        <v>350</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>220</v>
+        <v>266</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>286</v>
+        <v>335</v>
       </c>
       <c r="J66" s="2"/>
       <c r="K66" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="67" spans="1:11" ht="103.95" customHeight="1">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" ht="103.95" hidden="1" customHeight="1">
       <c r="A67" s="3" t="s">
-        <v>314</v>
+        <v>351</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>310</v>
+        <v>347</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>22</v>
+        <v>73</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>315</v>
+        <v>352</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>316</v>
+        <v>353</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>317</v>
+        <v>354</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>220</v>
+        <v>266</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>286</v>
+        <v>335</v>
       </c>
       <c r="J67" s="2"/>
       <c r="K67" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="68" spans="1:11" ht="103.95" customHeight="1">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" ht="103.95" hidden="1" customHeight="1">
       <c r="A68" s="3" t="s">
-        <v>318</v>
+        <v>355</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>319</v>
+        <v>356</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>320</v>
+        <v>357</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>321</v>
+        <v>358</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>322</v>
+        <v>359</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>220</v>
+        <v>266</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="J68" s="2"/>
       <c r="K68" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="69" spans="1:11" ht="103.95" customHeight="1">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" ht="103.95" hidden="1" customHeight="1">
       <c r="A69" s="3" t="s">
-        <v>324</v>
+        <v>360</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>325</v>
+        <v>361</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>326</v>
+        <v>23</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>327</v>
+        <v>362</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>328</v>
+        <v>363</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>329</v>
+        <v>364</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>220</v>
+        <v>266</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="J69" s="2"/>
       <c r="K69" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="70" spans="1:11" ht="103.95" customHeight="1">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" ht="103.95" hidden="1" customHeight="1">
       <c r="A70" s="3" t="s">
-        <v>330</v>
+        <v>365</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>331</v>
+        <v>361</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>332</v>
+        <v>366</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>333</v>
+        <v>367</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>334</v>
+        <v>368</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>220</v>
+        <v>266</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="J70" s="2"/>
       <c r="K70" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="71" spans="1:11" ht="103.95" customHeight="1"/>
-    <row r="72" spans="1:11" ht="103.95" customHeight="1"/>
-    <row r="73" spans="1:11" ht="103.95" customHeight="1"/>
+        <v>170</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" ht="103.95" hidden="1" customHeight="1">
+      <c r="A71" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="F71" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="G71" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="I71" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="J71" s="2"/>
+      <c r="K71" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" ht="103.95" hidden="1" customHeight="1">
+      <c r="A72" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="G72" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="I72" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="J72" s="2"/>
+      <c r="K72" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" ht="103.95" hidden="1" customHeight="1">
+      <c r="A73" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="G73" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="I73" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="J73" s="2"/>
+      <c r="K73" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" ht="103.95" hidden="1" customHeight="1">
+      <c r="A74" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="F74" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="G74" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I74" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="J74" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="K74" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" ht="103.95" hidden="1" customHeight="1">
+      <c r="A75" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="F75" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="G75" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I75" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="J75" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="K75" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" ht="103.95" hidden="1" customHeight="1">
+      <c r="A76" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="F76" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="G76" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="I76" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="J76" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="K76" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" ht="103.95" hidden="1" customHeight="1">
+      <c r="A77" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="F77" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="G77" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="I77" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="J77" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="K77" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" ht="103.95" hidden="1" customHeight="1">
+      <c r="A78" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="F78" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="G78" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="I78" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="J78" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="K78" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" ht="103.95" hidden="1" customHeight="1">
+      <c r="A79" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="F79" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="G79" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="I79" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="J79" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="K79" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" ht="103.95" hidden="1" customHeight="1">
+      <c r="A80" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="F80" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="G80" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="I80" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="J80" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="K80" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" ht="103.95" hidden="1" customHeight="1">
+      <c r="A81" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="F81" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="G81" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I81" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="J81" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="K81" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" ht="103.95" hidden="1" customHeight="1">
+      <c r="A82" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="F82" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="G82" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I82" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="J82" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="K82" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="H2:H70">
-    <cfRule type="expression" dxfId="5" priority="4">
+    <cfRule type="expression" dxfId="11" priority="4">
       <formula>H2="Must Have"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="5">
+    <cfRule type="expression" dxfId="10" priority="5">
       <formula>H2="Should Have"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="3" priority="6">
+    <cfRule type="expression" dxfId="9" priority="6">
       <formula>H2="Could Have"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K70">
-    <cfRule type="expression" dxfId="2" priority="1">
+  <conditionalFormatting sqref="H71:H82">
+    <cfRule type="expression" dxfId="8" priority="7">
+      <formula>H2="Must Have"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="7" priority="7">
+      <formula>H2="Should Have"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="6" priority="7">
+      <formula>H2="Could Have"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K2:K73">
+    <cfRule type="expression" dxfId="5" priority="1">
       <formula>K2="Done"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="2">
+    <cfRule type="expression" dxfId="4" priority="2">
       <formula>K2="In Progress"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="3">
+    <cfRule type="expression" dxfId="3" priority="3">
       <formula>K2="Blocked"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="K74:K82">
+    <cfRule type="expression" dxfId="2" priority="8">
+      <formula>K5="Done"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="8">
+      <formula>K5="In Progress"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="0" priority="8">
+      <formula>K5="Blocked"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" sqref="H2:H70" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" sqref="H2:H82" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Must Have,Should Have,Could Have"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="K2:K70" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" sqref="K2:K82" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"Not Started,In Progress,Blocked,Done"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3977,28 +4863,28 @@
   <sheetData>
     <row r="1" spans="1:6" ht="40.049999999999997" customHeight="1">
       <c r="A1" s="6" t="s">
-        <v>335</v>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
+        <v>434</v>
+      </c>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>336</v>
+        <v>435</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>337</v>
+        <v>436</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>338</v>
+        <v>437</v>
       </c>
       <c r="B4">
-        <v>72</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -4006,20 +4892,20 @@
         <v>18</v>
       </c>
       <c r="B5">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>115</v>
+        <v>56</v>
       </c>
       <c r="B6">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" t="s">
-        <v>220</v>
+        <v>266</v>
       </c>
       <c r="B7">
         <v>17</v>
@@ -4027,10 +4913,18 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" t="s">
-        <v>339</v>
+        <v>438</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" t="s">
+        <v>439</v>
+      </c>
+      <c r="B9">
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -4038,13 +4932,13 @@
         <v>8</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>340</v>
+        <v>440</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>341</v>
+        <v>441</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>342</v>
+        <v>442</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -4052,150 +4946,150 @@
         <v>19</v>
       </c>
       <c r="B11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C11" t="s">
-        <v>343</v>
+        <v>443</v>
       </c>
       <c r="D11" t="s">
-        <v>344</v>
+        <v>444</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" t="s">
-        <v>36</v>
+        <v>64</v>
       </c>
       <c r="B12">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C12" t="s">
-        <v>345</v>
+        <v>445</v>
       </c>
       <c r="D12" t="s">
-        <v>344</v>
+        <v>444</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" t="s">
-        <v>97</v>
+        <v>132</v>
       </c>
       <c r="B13">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C13" t="s">
-        <v>346</v>
+        <v>446</v>
       </c>
       <c r="D13" t="s">
-        <v>344</v>
+        <v>444</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" t="s">
-        <v>147</v>
+        <v>192</v>
       </c>
       <c r="B14">
         <v>8</v>
       </c>
       <c r="C14" t="s">
-        <v>347</v>
+        <v>447</v>
       </c>
       <c r="D14" t="s">
-        <v>344</v>
+        <v>444</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" t="s">
-        <v>181</v>
+        <v>226</v>
       </c>
       <c r="B15">
         <v>9</v>
       </c>
       <c r="C15" t="s">
-        <v>348</v>
+        <v>448</v>
       </c>
       <c r="D15" t="s">
-        <v>349</v>
+        <v>449</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" t="s">
-        <v>221</v>
+        <v>267</v>
       </c>
       <c r="B16">
         <v>5</v>
       </c>
       <c r="C16" t="s">
-        <v>350</v>
+        <v>450</v>
       </c>
       <c r="D16" t="s">
-        <v>349</v>
+        <v>449</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>243</v>
+        <v>289</v>
       </c>
       <c r="B17">
         <v>9</v>
       </c>
       <c r="C17" t="s">
-        <v>351</v>
+        <v>451</v>
       </c>
       <c r="D17" t="s">
-        <v>349</v>
+        <v>449</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>286</v>
+        <v>335</v>
       </c>
       <c r="B18">
         <v>8</v>
       </c>
       <c r="C18" t="s">
-        <v>352</v>
+        <v>452</v>
       </c>
       <c r="D18" t="s">
-        <v>349</v>
+        <v>449</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>323</v>
+        <v>374</v>
       </c>
       <c r="B19">
         <v>3</v>
       </c>
       <c r="C19" t="s">
-        <v>353</v>
+        <v>453</v>
       </c>
       <c r="D19" t="s">
-        <v>349</v>
+        <v>449</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="5" t="s">
-        <v>354</v>
+        <v>454</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>355</v>
+        <v>455</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>356</v>
+        <v>456</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>357</v>
+        <v>457</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>358</v>
+        <v>458</v>
       </c>
     </row>
   </sheetData>
